--- a/artfynd/A 40133-2026 artfynd.xlsx
+++ b/artfynd/A 40133-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,47 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137495251</v>
+        <v>137522974</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>93524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kajsätterskärret, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610149</v>
+        <v>610159</v>
       </c>
       <c r="R2" t="n">
-        <v>6509633</v>
+        <v>6509610</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,19 +748,9 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,13 +776,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495251</t>
+          <t>https://artportalen.se/Sighting/137522974</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137495843</v>
+        <v>137495251</v>
       </c>
       <c r="B3" t="n">
         <v>58032</v>
@@ -823,6 +811,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610176</v>
+        <v>610149</v>
       </c>
       <c r="R3" t="n">
-        <v>6509729</v>
+        <v>6509633</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -865,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,6 +889,119 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495251</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137495843</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kajsätterskärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>610176</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6509729</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bergshammar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137495843</t>
         </is>
@@ -909,6 +1011,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40133-2026 artfynd.xlsx
+++ b/artfynd/A 40133-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137522974</v>
       </c>
       <c r="B2" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137495251</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>137495843</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
